--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_096_Brunei_Darussalam.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_096_Brunei_Darussalam.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R781a65bdbf534d29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rc09c4f4377d6448c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R415ce81a7beb4f73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R7beae19b4c704cc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rfae845ae78e24cd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R0dc20c55410547a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rcd8f7f4c2ca14986"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rbed4c696e7094e97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R85a7b0bf4c324085"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R2d36fc61e27c4908"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rcd98e3fadd6f4d6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R1e1605b529d3472a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ096CommercialTable" displayName="EEZ096CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ096CommercialTable" displayName="EEZ096CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ096FunctionalTable" displayName="EEZ096FunctionalTable" ref="A1:O19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O19"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ096FunctionalTable" displayName="EEZ096FunctionalTable" ref="A1:E19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E19"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ096ValidationTable" displayName="EEZ096ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ096ValidationTable" displayName="EEZ096ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -7193,7 +7147,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R058a8ab186554ce1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf1ac4ef46914a98"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7203,20 +7157,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7224,552 +7168,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>370.0370501311</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.44</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>275.4228703338166</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>370.0370501311</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>275.4228703338166</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$98,A2,'Species'!$U$2:$U$98))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>101916.66647696594</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.44</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>275.4228703338166</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>101916.66647696594</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>3117.9177139594003</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.846623379821355</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>70.24628798530476</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>3117.9177139594003</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>86.02270930982456</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$98,A3,'Species'!$U$2:$U$98))</x:f>
-        <x:v>268211.72915988223</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.846623379821355</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>70.24628798530476</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>219022.1456492751</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>49189.58351060713</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.2245872597256693</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.22458725972566937</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>15.4558671537</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.379906951211427</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2398.319017515802</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>15.4558671537</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2427.562700139313</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$98,A4,'Species'!$U$2:$U$98))</x:f>
-        <x:v>37520.08660063049</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.379906951211427</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2398.319017515802</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>37068.100126916535</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>451.9864737139578</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0121934081370885</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.012193408137088567</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1316.8157937692001</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.089401225621146</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>122.85737323987159</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1316.8157937692001</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>261.14858456635255</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$98,A5,'Species'!$U$2:$U$98))</x:f>
-        <x:v>343884.58067744464</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.089401225621146</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>122.85737323987159</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>161780.5294632604</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>182104.05121418423</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>2.1256240279244434</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>1.1256240279244432</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.3521378622</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.3521378622</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$98,A6,'Species'!$U$2:$U$98))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>4.433153031784528</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>4.433153031784528</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>4978.7644926692</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.3354533617752793</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>216.49773731923935</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>4978.7644926692</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>351.1933227320069</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$98,A7,'Species'!$U$2:$U$98))</x:f>
-        <x:v>1748508.845280631</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.3354533617752793</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>216.49773731923935</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1077891.2473082524</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>670617.5979723786</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.6221570122654472</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.6221570122654473</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>5833.6187834547</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6227230276068165</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>419.49136699378596</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>5833.6187834547</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>775.7403720645141</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$98,A8,'Species'!$U$2:$U$98))</x:f>
-        <x:v>4525373.605559687</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6227230276068165</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>419.49136699378596</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>2447152.717992039</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>2078220.8875676482</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.8492403732256195</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.8492403732256194</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>114.5800142749</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.05</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1122.018454301963</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>114.5800142749</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1122.018454301963</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$98,A9,'Species'!$U$2:$U$98))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>128560.89051062014</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.05</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1122.018454301963</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>128560.89051062014</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>944.9191326857999</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.382025973137981</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2410.0495582589465</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>944.9191326857999</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2437.47005575684</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$98,A10,'Species'!$U$2:$U$98))</x:f>
-        <x:v>2303212.0910333614</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.382025973137981</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2410.0495582589465</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2277301.938319839</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>25910.152713522315</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0113775658280248</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.011377565828024743</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f33847db34f4fe5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf88bf1a05be4191"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7779,20 +7364,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7800,1038 +7375,364 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>91.3055921673</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.8126978516224574</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>649.6775378916402</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>91.3055921673</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>779.3302593107586</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$98,A2,'Species'!$U$2:$U$98))</x:f>
-        <x:v>71157.21082026428</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.8126978516224574</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>649.6775378916402</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>59319.1923149897</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>11838.018505274587</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1995647284341593</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.1995647284341593</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>209.9727457349</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.42</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2630.2679918953813</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>209.9727457349</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2630.2679918953813</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$98,A3,'Species'!$U$2:$U$98))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>552284.592276895</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.42</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2630.2679918953813</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>552284.592276895</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>70.4970647042</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.284346426143778</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1924.6263443834628</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>70.4970647042</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1995.749597158972</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$98,A4,'Species'!$U$2:$U$98))</x:f>
-        <x:v>140694.48848429712</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.284346426143778</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1924.6263443834628</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>135680.50793140888</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>5013.9805528882425</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0369543173837688</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.03695431738376879</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1280.3456903582999</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.4239849322635045</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2654.5134627090138</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1280.3456903582999</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2688.467532960701</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$98,A5,'Species'!$U$2:$U$98))</x:f>
-        <x:v>3442167.8194944444</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.4239849322635045</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2654.5134627090138</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>3398694.8719775733</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>43472.94751687115</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.012791071030032</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.012791071030032146</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.01</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>3162.2776601683795</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$98,A6,'Species'!$U$2:$U$98))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>31.622776601683796</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.5</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>31.622776601683796</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>114.5800142749</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.05</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1122.018454301963</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>114.5800142749</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1122.018454301963</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$98,A7,'Species'!$U$2:$U$98))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>128560.89051062014</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.05</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1122.018454301963</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>128560.89051062014</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>4.019844013</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>2.482383495859296</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>30.36571389915178</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>4.019844013</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>30.390419329424386</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$98,A8,'Species'!$U$2:$U$98))</x:f>
-        <x:v>122.1647451939461</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>2.482383495859296</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>30.36571389915178</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>122.06543321797616</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0.09931197596993968</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0008135962274642</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0008135962274642903</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>4.103844925700001</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.02259901600794</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>105.34138305049606</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>4.103844925700001</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>127.98209323629169</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$98,A9,'Species'!$U$2:$U$98))</x:f>
-        <x:v>525.21866390822</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.02259901600794</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>105.34138305049606</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>432.30470029799835</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>92.91396361022169</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.2149270261141594</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.21492702611415926</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>4735.5914537416</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.3671293648948226</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>232.87848380660662</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>4735.5914537416</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>354.79976989172985</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$98,A10,'Species'!$U$2:$U$98))</x:f>
-        <x:v>1680186.7580887622</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.3671293648948226</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>232.87848380660662</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1102817.3576748678</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>577369.4004138943</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.523540363593111</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.5235403635931111</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>2600.333265473601</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.5120794791030145</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>325.1467962099851</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>2600.333265473601</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>604.1685872810692</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$98,A11,'Species'!$U$2:$U$98))</x:f>
-        <x:v>1571039.6754611551</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.5120794791030145</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>325.1467962099851</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>845490.03034699</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>725549.6451141651</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.8581409822377193</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.8581409822377194</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>1277.7627169354</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.7189296374724723</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>523.5156119624824</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>1277.7627169354</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>717.1694380810429</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$98,A12,'Species'!$U$2:$U$98))</x:f>
-        <x:v>916372.3697054675</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.7189296374724723</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>523.5156119624824</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>668928.73069928</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>247443.63900618744</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.3699103172732865</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.3699103172732864</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>207.9639353901</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>2.429441222852857</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>26.880740161667518</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>207.9639353901</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>26.891090178993203</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$98,A13,'Species'!$U$2:$U$98))</x:f>
-        <x:v>5592.376940553495</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>2.429441222852857</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>26.880740161667518</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>5590.22451021909</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>2.152430334404926</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0003850346851848</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.0003850346851848654</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>3113.8978699464</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.8470935903349925</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>70.32238480915755</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>3113.8978699464</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>86.0945270563106</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$98,A14,'Species'!$U$2:$U$98))</x:f>
-        <x:v>268089.56441468827</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.8470935903349925</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>70.32238480915755</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>218976.7242667868</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>49112.84014790147</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.2242833813152927</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.2242833813152928</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>646.1391047159</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.2312361841998007</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>170.30844521928395</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>646.1391047159</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>170.42124812153156</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$98,A15,'Species'!$U$2:$U$98))</x:f>
-        <x:v>110115.83268581265</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.2312361841998007</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>170.30844521928395</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>110042.94631954502</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>72.88636626763036</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0006623447363538</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.000662344736353945</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>388.7679728146</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.645713881237363</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>442.29688550699063</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>388.7679728146</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>453.62940077300067</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$98,A16,'Species'!$U$2:$U$98))</x:f>
-        <x:v>176356.58254762122</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.645713881237363</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>442.29688550699063</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>171950.86356076397</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>4405.718986857246</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0256219648777767</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.02562196487777657</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>1581.9413690938998</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.090619744433225</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>123.20256351702065</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>1581.9413690938998</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>148.6139499786966</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$98,A17,'Species'!$U$2:$U$98))</x:f>
-        <x:v>235098.55549575167</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.090619744433225</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>123.20256351702065</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>194899.2320059938</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>40199.323489757866</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.2062569620003512</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.20625696200035104</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>349.77263451669995</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.5399909438666857</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>346.7296201916503</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>349.77263451669995</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>346.7312956234042</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$98,A18,'Species'!$U$2:$U$98))</x:f>
-        <x:v>121277.1187395868</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.5399909438666857</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>346.7296201916503</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>121276.5327194083</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0.5860201785108075</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0000048320987198</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.0000048320987199284</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>15.4558671537</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>4.379906951211427</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>2398.319017515802</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>15.4558671537</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>2427.562700139313</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$98,A19,'Species'!$U$2:$U$98))</x:f>
-        <x:v>37520.08660063049</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>4.379906951211427</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>2398.319017515802</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>37068.100126916535</x:v>
       </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>451.9864737139578</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0121934081370885</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.012193408137088567</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G19">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O19">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c88b1b967b44806"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref27736de167411b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9006,7 +7907,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -9105,7 +8006,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>9457192.928452255</x:v>
+        <x:v>6450698.669000201</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9119,7 +8020,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>9457192.928452251</x:v>
+        <x:v>7752166.790152376</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9133,7 +8034,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>1.862645149230957e-9</x:v>
+        <x:v>-3006494.2594520524</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9147,7 +8048,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-1.862645149230957e-9</x:v>
+        <x:v>-1705026.1382998778</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9158,9 +8059,9 @@
         <x:v>EEZ_096</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -9172,47 +8073,19 @@
         <x:v>EEZ_096</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_096</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_096</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92ab78aa2f9f4c17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce1d422f9a394d16"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9259,7 +8132,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
